--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/aysen.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/aysen.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aysén" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Aysén" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,22 +514,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4144-166-CM25</t>
+          <t>1286962-6-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-11-LR24</t>
+          <t>2239-14-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.253.000-4</t>
+          <t>65.072.937-4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
+          <t>Corporación de Deportes y Recreación de la Municipalidad de Aysén</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>6123.76</v>
+        <v>1049.58</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1286962-2-CM26</t>
+          <t>4609-19-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>65.072.937-4</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corporación de Deportes y Recreación de la Municipalidad de Aysén</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SUPER SOFTWARE SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.486.150-7</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1769.11</v>
+        <v>29333.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3791-8-CM26</t>
+          <t>1195-72-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>28690.9</v>
+        <v>24276</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4609-42-CM26</t>
+          <t>5038-19-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SUPER SOFTWARE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.486.150-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>22463.39</v>
+        <v>33290.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1485465-11-CM26</t>
+          <t>3622-27-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">I. Municipalidad de O'Higgins </t>
+          <t>I MUNICIPALIDAD DE O HIGGINS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>13846.96</v>
+        <v>13854.46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1195-115-CM26</t>
+          <t>3951-121-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>21777</v>
+        <v>894.88</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2713-473-CM26</t>
+          <t>2713-309-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>44351.3</v>
+        <v>44387</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1195-439-CM26</t>
+          <t>1195-340-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,7 +996,743 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
+        <v>7090.02</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>734-761-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>61.607.800-3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>293475.42</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1195-536-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>69.240.300-2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>6806.42</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1182705-225-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>65.199.131-5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACIÓN TÉCNICA DE LA REGIÓN DE AYSÉN DEL GENERAL CARLOS I</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>33834.08</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>4144-166-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69.253.000-4</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>6123.76</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1286962-2-CM26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>65.072.937-4</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Corporación de Deportes y Recreación de la Municipalidad de Aysén</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>1769.11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3791-8-CM26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69.240.200-6</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CISNES</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>28690.9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4609-42-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.240.400-9</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>SUPER SOFTWARE SPA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>76.486.150-7</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>22463.39</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1485465-11-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>69.253.500-6</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I. Municipalidad de O'Higgins </t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>13846.96</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1195-115-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>69.240.300-2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>NETSUS SPA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>21777</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2713-473-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>44351.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1195-439-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>69.240.300-2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
         <v>6062.46</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>5019-215-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>65.224.300-2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>1267.85</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/aysen.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">I. Municipalidad de O'Higgins </t>
+          <t>I MUNICIPALIDAD DE O HIGGINS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1733,6 +1733,71 @@
       </c>
       <c r="M21" s="2" t="n">
         <v>1267.85</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>734-655-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>61.607.800-3</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Inversiones Hebo Limitada</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>293254.08</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/aysen.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/aysen.xlsx
@@ -562,7 +562,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.486.150-7</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1115,7 +1147,11 @@
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1176,7 +1212,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1237,7 +1277,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1298,7 +1342,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1407,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1420,7 +1472,11 @@
           <t>76.486.150-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1481,7 +1537,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1602,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1603,7 +1667,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1732,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1725,7 +1797,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
